--- a/diseases/d174/2026-2029.xlsx
+++ b/diseases/d174/2026-2029.xlsx
@@ -1158,7 +1158,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9388,7 +9388,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11546,7 +11546,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12498,7 +12498,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">

--- a/diseases/d174/2026-2029.xlsx
+++ b/diseases/d174/2026-2029.xlsx
@@ -1158,7 +1158,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9388,7 +9388,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11546,7 +11546,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12498,7 +12498,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">

--- a/diseases/d174/2026-2029.xlsx
+++ b/diseases/d174/2026-2029.xlsx
@@ -13937,6 +13937,408 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>D174</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>marburg-virus-disease</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Marburg virus disease</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>D174</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Marburg virus disease</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>马堡病毒病</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SER_JP_MARBURG_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP70" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ70" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>SER_JP_MARBURG_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV70" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA70" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB70" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC70" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>D174</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>marburg-virus-disease</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Marburg virus disease</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>D174</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Marburg virus disease</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>马堡病毒病</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SER_JP_MARBURG_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>SER_JP_MARBURG_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Marburg hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Japan NIID Marburg virus disease notifications.</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN71" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>SER_JP_MARBURG_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV71" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA71" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC71" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13970,7 +14372,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -14053,7 +14455,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -14063,7 +14465,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">
@@ -14083,7 +14485,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d174/2026-2029.xlsx
+++ b/diseases/d174/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -916,9 +913,6 @@
       <c r="P3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1168,7 +1162,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN4" t="b">
@@ -1318,9 +1312,6 @@
       <c r="P5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1570,7 +1561,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -1720,9 +1711,6 @@
       <c r="P7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1972,7 +1960,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2122,9 +2110,6 @@
       <c r="P9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2374,7 +2359,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -2524,9 +2509,6 @@
       <c r="P11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2776,7 +2758,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -2923,9 +2905,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -3074,9 +3053,6 @@
       <c r="P14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3326,7 +3302,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3476,9 +3452,6 @@
       <c r="P16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -3728,7 +3701,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -3878,9 +3851,6 @@
       <c r="P18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -4130,7 +4100,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4280,9 +4250,6 @@
       <c r="P20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4532,7 +4499,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4679,9 +4646,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -4830,9 +4794,6 @@
       <c r="P23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -5082,7 +5043,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -5232,9 +5193,6 @@
       <c r="P25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -5484,7 +5442,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -5634,9 +5592,6 @@
       <c r="P27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -5886,7 +5841,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -6036,9 +5991,6 @@
       <c r="P29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -6288,7 +6240,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -6435,9 +6387,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -6586,9 +6535,6 @@
       <c r="P32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -6838,7 +6784,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -6988,9 +6934,6 @@
       <c r="P34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -7240,7 +7183,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7390,9 +7333,6 @@
       <c r="P36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -7642,7 +7582,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -7792,9 +7732,6 @@
       <c r="P38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -8044,7 +7981,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8191,9 +8128,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -8342,9 +8276,6 @@
       <c r="P41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -8594,7 +8525,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN42" t="b">
@@ -8744,9 +8675,6 @@
       <c r="P43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -8996,7 +8924,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN44" t="b">
@@ -9146,9 +9074,6 @@
       <c r="P45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -9398,7 +9323,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -9548,9 +9473,6 @@
       <c r="P47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -9800,7 +9722,7 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN48" t="b">
@@ -9950,9 +9872,6 @@
       <c r="P49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -10202,7 +10121,7 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN50" t="b">
@@ -10349,9 +10268,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -10500,9 +10416,6 @@
       <c r="P52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -10752,7 +10665,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -10902,9 +10815,6 @@
       <c r="P54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -11154,7 +11064,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11304,9 +11214,6 @@
       <c r="P56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -11556,7 +11463,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -11706,9 +11613,6 @@
       <c r="P58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -11958,7 +11862,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12105,9 +12009,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -12256,9 +12157,6 @@
       <c r="P61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -12508,7 +12406,7 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN62" t="b">
@@ -12658,9 +12556,6 @@
       <c r="P63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -12910,7 +12805,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -13060,9 +12955,6 @@
       <c r="P65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -13312,7 +13204,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -13462,9 +13354,6 @@
       <c r="P67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -13714,7 +13603,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -13861,9 +13750,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -14012,9 +13898,6 @@
       <c r="P70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -14264,7 +14147,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">

--- a/diseases/d174/2026-2029.xlsx
+++ b/diseases/d174/2026-2029.xlsx
@@ -14222,6 +14222,405 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>D174</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>marburg-virus-disease</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Marburg virus disease</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>D174</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Marburg virus disease</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>马堡病毒病</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SER_JP_MARBURG_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>SER_JP_MARBURG_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV72" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA72" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC72" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>D174</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>marburg-virus-disease</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Marburg virus disease</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>D174</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Marburg virus disease</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>马堡病毒病</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SER_JP_MARBURG_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>SER_JP_MARBURG_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Marburg hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Japan NIID Marburg virus disease notifications.</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN73" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>SER_JP_MARBURG_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA73" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC73" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14255,7 +14654,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -14338,7 +14737,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
@@ -14348,7 +14747,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11">
@@ -14368,7 +14767,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d174/2026-2029.xlsx
+++ b/diseases/d174/2026-2029.xlsx
@@ -14621,6 +14621,405 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>D174</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>marburg-virus-disease</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Marburg virus disease</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>D174</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Marburg virus disease</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>马堡病毒病</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SER_JP_MARBURG_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>SER_JP_MARBURG_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV74" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>D174</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>marburg-virus-disease</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Marburg virus disease</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>D174</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Marburg virus disease</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>马堡病毒病</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SER_JP_MARBURG_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>SER_JP_MARBURG_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Marburg hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Japan NIID Marburg virus disease notifications.</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN75" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>SER_JP_MARBURG_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV75" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA75" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14654,7 +15053,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -14737,7 +15136,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -14747,7 +15146,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11">
@@ -14767,7 +15166,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d174/2026-2029.xlsx
+++ b/diseases/d174/2026-2029.xlsx
@@ -1152,7 +1152,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9712,7 +9712,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11054,7 +11054,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11852,7 +11852,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -12795,7 +12795,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13593,7 +13593,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -14137,7 +14137,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14935,7 +14935,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">

--- a/diseases/d174/2026-2029.xlsx
+++ b/diseases/d174/2026-2029.xlsx
@@ -1152,7 +1152,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9712,7 +9712,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11054,7 +11054,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11852,7 +11852,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -12795,7 +12795,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13593,7 +13593,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -14137,7 +14137,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14935,7 +14935,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">

--- a/diseases/d174/2026-2029.xlsx
+++ b/diseases/d174/2026-2029.xlsx
@@ -1152,7 +1152,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9712,7 +9712,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11054,7 +11054,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11852,7 +11852,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -12795,7 +12795,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13593,7 +13593,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -14137,7 +14137,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14935,7 +14935,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">

--- a/diseases/d174/2026-2029.xlsx
+++ b/diseases/d174/2026-2029.xlsx
@@ -1152,7 +1152,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9712,7 +9712,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11054,7 +11054,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11852,7 +11852,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -12795,7 +12795,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13593,7 +13593,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -14137,7 +14137,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14935,7 +14935,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">

--- a/diseases/d174/2026-2029.xlsx
+++ b/diseases/d174/2026-2029.xlsx
@@ -15020,6 +15020,550 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>D174</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>marburg-virus-disease</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Marburg virus disease</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>D174</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Marburg virus disease</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>马堡病毒病</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SER_JP_MARBURG_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>SER_JP_MARBURG_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV76" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA76" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC76" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>D174</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>marburg-virus-disease</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Marburg virus disease</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>D174</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Marburg virus disease</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>马堡病毒病</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SER_JP_MARBURG_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>SER_JP_MARBURG_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Marburg hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Japan NIID Marburg virus disease notifications.</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN77" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>SER_JP_MARBURG_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D174</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>marburg-virus-disease</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Marburg virus disease</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D174</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Marburg virus disease</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>马堡病毒病</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr"/>
+      <c r="AT78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15053,7 +15597,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -15136,7 +15680,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
@@ -15146,7 +15690,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11">
@@ -15166,7 +15710,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
